--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="262">
   <si>
     <t/>
   </si>
@@ -103,189 +103,177 @@
     <t>SOFTX GRVTY 23CM 28S</t>
   </si>
   <si>
-    <t>20141368</t>
-  </si>
-  <si>
-    <t>HERS CL.BRZ 17S-23.5</t>
+    <t>20120202</t>
+  </si>
+  <si>
+    <t>LAURIER P/LINER NC40</t>
+  </si>
+  <si>
+    <t>10014567</t>
+  </si>
+  <si>
+    <t>LAURIER PL CLNF NP40</t>
+  </si>
+  <si>
+    <t>20106050</t>
+  </si>
+  <si>
+    <t>CHARM PL CL.FRSH 32S</t>
+  </si>
+  <si>
+    <t>20118829</t>
+  </si>
+  <si>
+    <t>CHRM PL COOL FRS 28S</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20132372</t>
+  </si>
+  <si>
+    <t>CHARM PL SRH+HBL 32S</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20090918</t>
+  </si>
+  <si>
+    <t>SOFTEX PL D.SRH 20'S</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>20038185</t>
+  </si>
+  <si>
+    <t>SOFTEX PL DS NP 44'S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20081895</t>
+  </si>
+  <si>
+    <t>SOFTEX PL D.SRH 30'S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20106051</t>
+  </si>
+  <si>
+    <t>SOFTEX DS WG 30'S/23</t>
+  </si>
+  <si>
+    <t>20038184</t>
+  </si>
+  <si>
+    <t>SOFTEX D.SRH WG 20'S</t>
+  </si>
+  <si>
+    <t>20140429</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT DS 17/29</t>
+  </si>
+  <si>
+    <t>20140420</t>
+  </si>
+  <si>
+    <t>CHARM NGHT DS 11S/35</t>
+  </si>
+  <si>
+    <t>20130843</t>
+  </si>
+  <si>
+    <t>CHARM DN SRH+HBL 10S</t>
+  </si>
+  <si>
+    <t>20106053</t>
+  </si>
+  <si>
+    <t>SOFTEX DS WG 24'S/29</t>
+  </si>
+  <si>
+    <t>20077515</t>
+  </si>
+  <si>
+    <t>SOFTEX DS S.WG 16'S</t>
+  </si>
+  <si>
+    <t>20130846</t>
+  </si>
+  <si>
+    <t>SOFTEX DN.SRH 18S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20067253</t>
+  </si>
+  <si>
+    <t>SOFTEX DS S.WG 12'S</t>
+  </si>
+  <si>
+    <t>20130848</t>
+  </si>
+  <si>
+    <t>SOFTEX DN.SRH 8S</t>
+  </si>
+  <si>
+    <t>20090955</t>
+  </si>
+  <si>
+    <t>SOFTEX D.SRH NW 18'S</t>
+  </si>
+  <si>
+    <t>20090167</t>
+  </si>
+  <si>
+    <t>CHARM EX.COMF MW 18S</t>
+  </si>
+  <si>
+    <t>20076572</t>
+  </si>
+  <si>
+    <t>CHARM EX.COMF MW 16S</t>
+  </si>
+  <si>
+    <t>20118830</t>
+  </si>
+  <si>
+    <t>CHRM DN SRH+HRBL 16S</t>
+  </si>
+  <si>
+    <t>20019342</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GUARD 10</t>
+  </si>
+  <si>
+    <t>20016076</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GUARD 20</t>
+  </si>
+  <si>
+    <t>20046527</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GRD DY16</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20141367</t>
-  </si>
-  <si>
-    <t>HERS CL BRZE 12'S-30</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20120202</t>
-  </si>
-  <si>
-    <t>LAURIER P/LINER NC40</t>
-  </si>
-  <si>
-    <t>10014567</t>
-  </si>
-  <si>
-    <t>LAURIER PL CLNF NP40</t>
-  </si>
-  <si>
-    <t>20106050</t>
-  </si>
-  <si>
-    <t>CHARM PL CL.FRSH 32S</t>
-  </si>
-  <si>
-    <t>20118829</t>
-  </si>
-  <si>
-    <t>CHRM PL COOL FRS 28S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20132372</t>
-  </si>
-  <si>
-    <t>CHARM PL SRH+HBL 32S</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20090918</t>
-  </si>
-  <si>
-    <t>SOFTEX PL D.SRH 20'S</t>
-  </si>
-  <si>
-    <t>20038185</t>
-  </si>
-  <si>
-    <t>SOFTEX PL DS NP 44'S</t>
-  </si>
-  <si>
-    <t>20081895</t>
-  </si>
-  <si>
-    <t>SOFTEX PL D.SRH 30'S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20106051</t>
-  </si>
-  <si>
-    <t>SOFTEX DS WG 30'S/23</t>
-  </si>
-  <si>
-    <t>20038184</t>
-  </si>
-  <si>
-    <t>SOFTEX D.SRH WG 20'S</t>
-  </si>
-  <si>
-    <t>20140429</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT DS 17/29</t>
-  </si>
-  <si>
-    <t>20140420</t>
-  </si>
-  <si>
-    <t>CHARM NGHT DS 11S/35</t>
-  </si>
-  <si>
-    <t>20130843</t>
-  </si>
-  <si>
-    <t>CHARM DN SRH+HBL 10S</t>
-  </si>
-  <si>
-    <t>20106053</t>
-  </si>
-  <si>
-    <t>SOFTEX DS WG 24'S/29</t>
-  </si>
-  <si>
-    <t>20077515</t>
-  </si>
-  <si>
-    <t>SOFTEX DS S.WG 16'S</t>
-  </si>
-  <si>
-    <t>20130846</t>
-  </si>
-  <si>
-    <t>SOFTEX DN.SRH 18S</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20067253</t>
-  </si>
-  <si>
-    <t>SOFTEX DS S.WG 12'S</t>
-  </si>
-  <si>
-    <t>20130848</t>
-  </si>
-  <si>
-    <t>SOFTEX DN.SRH 8S</t>
-  </si>
-  <si>
-    <t>20090955</t>
-  </si>
-  <si>
-    <t>SOFTEX D.SRH NW 18'S</t>
-  </si>
-  <si>
-    <t>20090167</t>
-  </si>
-  <si>
-    <t>CHARM EX.COMF MW 18S</t>
-  </si>
-  <si>
-    <t>20076572</t>
-  </si>
-  <si>
-    <t>CHARM EX.COMF MW 16S</t>
-  </si>
-  <si>
-    <t>20118830</t>
-  </si>
-  <si>
-    <t>CHRM DN SRH+HRBL 16S</t>
-  </si>
-  <si>
-    <t>20019342</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GUARD 10</t>
-  </si>
-  <si>
-    <t>20016076</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GUARD 20</t>
-  </si>
-  <si>
-    <t>20046527</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GRD DY16</t>
-  </si>
-  <si>
     <t>20125494</t>
   </si>
   <si>
@@ -692,12 +680,6 @@
   </si>
   <si>
     <t>18</t>
-  </si>
-  <si>
-    <t>20026897</t>
-  </si>
-  <si>
-    <t>TESSA FAC.TISSUE 260</t>
   </si>
   <si>
     <t>20034036</t>
@@ -1207,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1449,41 +1431,41 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1492,18 +1474,18 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1512,18 +1494,18 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1532,18 +1514,18 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1552,18 +1534,18 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1572,18 +1554,18 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1592,7 +1574,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>12</v>
@@ -1609,10 +1591,10 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -1629,10 +1611,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1640,10 +1622,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1652,18 +1634,18 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1672,18 +1654,18 @@
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1692,58 +1674,58 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1752,10 +1734,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1772,7 +1754,7 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>12</v>
@@ -1792,18 +1774,18 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1812,7 +1794,7 @@
         <v>18</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>12</v>
@@ -1820,122 +1802,122 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1949,13 +1931,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1969,13 +1951,13 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1989,13 +1971,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2009,13 +1991,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2029,13 +2011,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2049,13 +2031,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2069,13 +2051,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2089,13 +2071,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2109,13 +2091,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2129,13 +2111,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2149,53 +2131,53 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2209,10 +2191,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>19</v>
@@ -2229,13 +2211,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2249,10 +2231,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>19</v>
@@ -2269,13 +2251,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2289,13 +2271,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2309,53 +2291,53 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="E56" s="1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2369,13 +2351,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2389,13 +2371,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2409,10 +2391,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>12</v>
@@ -2420,39 +2402,39 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>12</v>
@@ -2469,13 +2451,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2489,70 +2471,70 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2569,10 +2551,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2589,10 +2571,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2609,13 +2591,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2629,13 +2611,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,50 +2631,50 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2709,10 +2691,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2729,10 +2711,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2749,13 +2731,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2769,30 +2751,30 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>12</v>
@@ -2800,19 +2782,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>12</v>
@@ -2829,10 +2811,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>12</v>
@@ -2849,13 +2831,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2869,13 +2851,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2889,50 +2871,50 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -2949,50 +2931,50 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>12</v>
@@ -3009,13 +2991,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3029,13 +3011,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3049,13 +3031,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3069,73 +3051,73 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>214</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3149,13 +3131,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3169,10 +3151,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>12</v>
@@ -3180,19 +3162,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>12</v>
@@ -3200,19 +3182,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>12</v>
@@ -3229,30 +3211,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>12</v>
@@ -3260,19 +3242,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>12</v>
@@ -3280,22 +3262,22 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3309,30 +3291,30 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>12</v>
@@ -3340,19 +3322,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>12</v>
@@ -3360,22 +3342,22 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3389,70 +3371,70 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3469,10 +3451,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3480,102 +3462,42 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B116" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -181,13 +181,13 @@
     <t>20140429</t>
   </si>
   <si>
-    <t>CHARM NIGHT DS 17/29</t>
+    <t>CHARM N DS 17S 29 CM</t>
   </si>
   <si>
     <t>20140420</t>
   </si>
   <si>
-    <t>CHARM NGHT DS 11S/35</t>
+    <t>CHARM N DS 11S 35 CM</t>
   </si>
   <si>
     <t>20130843</t>
@@ -301,7 +301,7 @@
     <t>20119730</t>
   </si>
   <si>
-    <t>HERS/P CNMRL 24'S-30</t>
+    <t>HERS/P CNMRL 30CM22S</t>
   </si>
   <si>
     <t>20131363</t>
@@ -517,7 +517,7 @@
     <t>20047284</t>
   </si>
   <si>
-    <t>CHARM NIGHT WG 12/35</t>
+    <t>CHARM N WG 12S 35 CM</t>
   </si>
   <si>
     <t>10032895</t>

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -166,6 +166,12 @@
     <t>8</t>
   </si>
   <si>
+    <t>20090955</t>
+  </si>
+  <si>
+    <t>SOFTEX D.SRH NW 18'S</t>
+  </si>
+  <si>
     <t>20106051</t>
   </si>
   <si>
@@ -178,372 +184,366 @@
     <t>SOFTEX D.SRH WG 20'S</t>
   </si>
   <si>
+    <t>20144230</t>
+  </si>
+  <si>
+    <t>CHARM M/WING 24S23CM</t>
+  </si>
+  <si>
+    <t>20144100</t>
+  </si>
+  <si>
+    <t>CRM DS NWING 26S23CM</t>
+  </si>
+  <si>
+    <t>20113228</t>
+  </si>
+  <si>
+    <t>SOFTEX DS 3IN1 16'S</t>
+  </si>
+  <si>
+    <t>20106053</t>
+  </si>
+  <si>
+    <t>SOFTEX DS WG 24'S/29</t>
+  </si>
+  <si>
+    <t>20077515</t>
+  </si>
+  <si>
+    <t>SOFTEX DS S.WG 16'S</t>
+  </si>
+  <si>
+    <t>20130846</t>
+  </si>
+  <si>
+    <t>SOFTEX DN.SRH 18S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20067253</t>
+  </si>
+  <si>
+    <t>SOFTEX DS S.WG 12'S</t>
+  </si>
+  <si>
+    <t>20130848</t>
+  </si>
+  <si>
+    <t>SOFTEX DN.SRH 8S</t>
+  </si>
+  <si>
+    <t>20131300</t>
+  </si>
+  <si>
+    <t>LAURIER NAT.C 16S-30</t>
+  </si>
+  <si>
+    <t>20090167</t>
+  </si>
+  <si>
+    <t>CHARM EX.COMF MW 18S</t>
+  </si>
+  <si>
+    <t>20076572</t>
+  </si>
+  <si>
+    <t>CHARM EX.COMF MW 16S</t>
+  </si>
+  <si>
+    <t>20019342</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GUARD 10</t>
+  </si>
+  <si>
+    <t>20016076</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GUARD 20</t>
+  </si>
+  <si>
+    <t>20046527</t>
+  </si>
+  <si>
+    <t>LAURIER SLM GRD DY16</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20122925</t>
+  </si>
+  <si>
+    <t>LRER NR.CL NT.W12/35</t>
+  </si>
+  <si>
+    <t>20125494</t>
+  </si>
+  <si>
+    <t>SFTEX PW CMF/NGT 12S</t>
+  </si>
+  <si>
+    <t>20133708</t>
+  </si>
+  <si>
+    <t>SFTEX PW CMF/NGHT18S</t>
+  </si>
+  <si>
+    <t>20119730</t>
+  </si>
+  <si>
+    <t>HERS/P CNMRL 30CM22S</t>
+  </si>
+  <si>
+    <t>20131363</t>
+  </si>
+  <si>
+    <t>HER'S PRTX CN WG 12S</t>
+  </si>
+  <si>
     <t>20140429</t>
   </si>
   <si>
     <t>CHARM N DS 17S 29 CM</t>
   </si>
   <si>
+    <t>10038967</t>
+  </si>
+  <si>
+    <t>NICE FC TISU LVG1000</t>
+  </si>
+  <si>
+    <t>20028457</t>
+  </si>
+  <si>
+    <t>MULTI FC.TISSUE 600G</t>
+  </si>
+  <si>
+    <t>20049293</t>
+  </si>
+  <si>
+    <t>PASEO KTCH TWL 70S</t>
+  </si>
+  <si>
+    <t>20094211</t>
+  </si>
+  <si>
+    <t>IDM SERBET SRBGN 25S</t>
+  </si>
+  <si>
+    <t>20046211</t>
+  </si>
+  <si>
+    <t>IDM WET TISSUE 50'S</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20107988</t>
+  </si>
+  <si>
+    <t>SANITER WIPES 50'S</t>
+  </si>
+  <si>
+    <t>20121228</t>
+  </si>
+  <si>
+    <t>NUVO WET TS BRU 50'S</t>
+  </si>
+  <si>
+    <t>20121229</t>
+  </si>
+  <si>
+    <t>NUVO WET TS MRH 50'S</t>
+  </si>
+  <si>
+    <t>20139610</t>
+  </si>
+  <si>
+    <t>NUVO WIPES NP 2X25S</t>
+  </si>
+  <si>
+    <t>20105673</t>
+  </si>
+  <si>
+    <t>PASEO WET TISSUE 25S</t>
+  </si>
+  <si>
+    <t>20027185</t>
+  </si>
+  <si>
+    <t>WETZ WIPES10 GRENTEA</t>
+  </si>
+  <si>
+    <t>20044874</t>
+  </si>
+  <si>
+    <t>DETTOL ASPTC WPS10'S</t>
+  </si>
+  <si>
+    <t>20141960</t>
+  </si>
+  <si>
+    <t>CHARM SFNGHT PNTS 2S</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20133707</t>
+  </si>
+  <si>
+    <t>CHARM SP.PANT L-XL2S</t>
+  </si>
+  <si>
+    <t>20092849</t>
+  </si>
+  <si>
+    <t>SFTX CLN MENST M-L2S</t>
+  </si>
+  <si>
+    <t>20136913</t>
+  </si>
+  <si>
+    <t>SFTX CLN MENST M-L5S</t>
+  </si>
+  <si>
+    <t>20121204</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 30/29</t>
+  </si>
+  <si>
+    <t>20045293</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NGH 8/30</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20021323</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 6/35</t>
+  </si>
+  <si>
+    <t>10036092</t>
+  </si>
+  <si>
+    <t>LAURIER RN WG 8'S/35</t>
+  </si>
+  <si>
+    <t>20135430</t>
+  </si>
+  <si>
+    <t>LAURIER RN 18'S 35CM</t>
+  </si>
+  <si>
+    <t>20048563</t>
+  </si>
+  <si>
+    <t>LAURIER R/N 8'S 40CM</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20114105</t>
+  </si>
+  <si>
+    <t>CHRM CL.FRSH 6S 42CM</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20099396</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH NW 8'S</t>
+  </si>
+  <si>
+    <t>20098616</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH NW 10S</t>
+  </si>
+  <si>
+    <t>20091792</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH WG 15S</t>
+  </si>
+  <si>
+    <t>20091786</t>
+  </si>
+  <si>
+    <t>CHARM CL.FRSH NW 17S</t>
+  </si>
+  <si>
+    <t>20130850</t>
+  </si>
+  <si>
+    <t>CHRM COOL.FRSH WG14S</t>
+  </si>
+  <si>
+    <t>20140121</t>
+  </si>
+  <si>
+    <t>SOFTX BR.COOL 23-14S</t>
+  </si>
+  <si>
+    <t>20017043</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 7/42</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20121205</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 18/35</t>
+  </si>
+  <si>
+    <t>20047284</t>
+  </si>
+  <si>
+    <t>CHARM N WG 12S 35 CM</t>
+  </si>
+  <si>
+    <t>10032895</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT GW 11/35</t>
+  </si>
+  <si>
+    <t>10005974</t>
+  </si>
+  <si>
+    <t>CHARM NIGHT WG 9S/29</t>
+  </si>
+  <si>
+    <t>20140120</t>
+  </si>
+  <si>
+    <t>SOFTX BRY COOL 36-8S</t>
+  </si>
+  <si>
     <t>20140420</t>
   </si>
   <si>
     <t>CHARM N DS 11S 35 CM</t>
   </si>
   <si>
-    <t>20130843</t>
-  </si>
-  <si>
-    <t>CHARM DN SRH+HBL 10S</t>
-  </si>
-  <si>
-    <t>20106053</t>
-  </si>
-  <si>
-    <t>SOFTEX DS WG 24'S/29</t>
-  </si>
-  <si>
-    <t>20077515</t>
-  </si>
-  <si>
-    <t>SOFTEX DS S.WG 16'S</t>
-  </si>
-  <si>
-    <t>20130846</t>
-  </si>
-  <si>
-    <t>SOFTEX DN.SRH 18S</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20067253</t>
-  </si>
-  <si>
-    <t>SOFTEX DS S.WG 12'S</t>
-  </si>
-  <si>
-    <t>20130848</t>
-  </si>
-  <si>
-    <t>SOFTEX DN.SRH 8S</t>
-  </si>
-  <si>
-    <t>20090955</t>
-  </si>
-  <si>
-    <t>SOFTEX D.SRH NW 18'S</t>
-  </si>
-  <si>
-    <t>20090167</t>
-  </si>
-  <si>
-    <t>CHARM EX.COMF MW 18S</t>
-  </si>
-  <si>
-    <t>20076572</t>
-  </si>
-  <si>
-    <t>CHARM EX.COMF MW 16S</t>
-  </si>
-  <si>
-    <t>20118830</t>
-  </si>
-  <si>
-    <t>CHRM DN SRH+HRBL 16S</t>
-  </si>
-  <si>
-    <t>20019342</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GUARD 10</t>
-  </si>
-  <si>
-    <t>20016076</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GUARD 20</t>
-  </si>
-  <si>
-    <t>20046527</t>
-  </si>
-  <si>
-    <t>LAURIER SLM GRD DY16</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20125494</t>
-  </si>
-  <si>
-    <t>SFTEX PW CMF/NGT 12S</t>
-  </si>
-  <si>
-    <t>20133708</t>
-  </si>
-  <si>
-    <t>SFTEX PW CMF/NGHT18S</t>
-  </si>
-  <si>
-    <t>20122925</t>
-  </si>
-  <si>
-    <t>LRER NR.CL NT.W12/35</t>
-  </si>
-  <si>
-    <t>20131300</t>
-  </si>
-  <si>
-    <t>LAURIER NAT.C 16S-30</t>
-  </si>
-  <si>
-    <t>20119730</t>
-  </si>
-  <si>
-    <t>HERS/P CNMRL 30CM22S</t>
-  </si>
-  <si>
-    <t>20131363</t>
-  </si>
-  <si>
-    <t>HER'S PRTX CN WG 12S</t>
-  </si>
-  <si>
-    <t>10038967</t>
-  </si>
-  <si>
-    <t>NICE FC TISU LVG1000</t>
-  </si>
-  <si>
-    <t>20028457</t>
-  </si>
-  <si>
-    <t>MULTI FC.TISSUE 600G</t>
-  </si>
-  <si>
-    <t>20049293</t>
-  </si>
-  <si>
-    <t>PASEO KTCH TWL 70S</t>
-  </si>
-  <si>
-    <t>20094211</t>
-  </si>
-  <si>
-    <t>IDM SERBET SRBGN 25S</t>
-  </si>
-  <si>
-    <t>20046211</t>
-  </si>
-  <si>
-    <t>IDM WET TISSUE 50'S</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20107988</t>
-  </si>
-  <si>
-    <t>SANITER WIPES 50'S</t>
-  </si>
-  <si>
-    <t>20121228</t>
-  </si>
-  <si>
-    <t>NUVO WET TS BRU 50'S</t>
-  </si>
-  <si>
-    <t>20121229</t>
-  </si>
-  <si>
-    <t>NUVO WET TS MRH 50'S</t>
-  </si>
-  <si>
-    <t>20139610</t>
-  </si>
-  <si>
-    <t>NUVO WIPES NP 2X25S</t>
-  </si>
-  <si>
-    <t>20105673</t>
-  </si>
-  <si>
-    <t>PASEO WET TISSUE 25S</t>
-  </si>
-  <si>
-    <t>20027185</t>
-  </si>
-  <si>
-    <t>WETZ WIPES10 GRENTEA</t>
-  </si>
-  <si>
-    <t>20044874</t>
-  </si>
-  <si>
-    <t>DETTOL ASPTC WPS10'S</t>
-  </si>
-  <si>
-    <t>20141960</t>
-  </si>
-  <si>
-    <t>CHARM SFNGHT PNTS 2S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20133707</t>
-  </si>
-  <si>
-    <t>CHARM SP.PANT L-XL2S</t>
-  </si>
-  <si>
-    <t>20092849</t>
-  </si>
-  <si>
-    <t>SFTX CLN MENST M-L2S</t>
-  </si>
-  <si>
-    <t>20136913</t>
-  </si>
-  <si>
-    <t>SFTX CLN MENST M-L5S</t>
-  </si>
-  <si>
-    <t>20121204</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 30/29</t>
-  </si>
-  <si>
-    <t>20045293</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NGH 8/30</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20021323</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 6/35</t>
-  </si>
-  <si>
-    <t>10036092</t>
-  </si>
-  <si>
-    <t>LAURIER RN WG 8'S/35</t>
-  </si>
-  <si>
-    <t>20135430</t>
-  </si>
-  <si>
-    <t>LAURIER RN 18'S 35CM</t>
-  </si>
-  <si>
-    <t>20048563</t>
-  </si>
-  <si>
-    <t>LAURIER R/N 8'S 40CM</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20114105</t>
-  </si>
-  <si>
-    <t>CHRM CL.FRSH 6S 42CM</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20099396</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH NW 8'S</t>
-  </si>
-  <si>
-    <t>20098616</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH NW 10S</t>
-  </si>
-  <si>
-    <t>20091792</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH WG 15S</t>
-  </si>
-  <si>
-    <t>20091786</t>
-  </si>
-  <si>
-    <t>CHARM CL.FRSH NW 17S</t>
-  </si>
-  <si>
-    <t>20130850</t>
-  </si>
-  <si>
-    <t>CHRM COOL.FRSH WG14S</t>
-  </si>
-  <si>
-    <t>20140121</t>
-  </si>
-  <si>
-    <t>SOFTX BR.COOL 23-14S</t>
-  </si>
-  <si>
-    <t>20017043</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 7/42</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20121205</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 18/35</t>
-  </si>
-  <si>
-    <t>20047284</t>
-  </si>
-  <si>
-    <t>CHARM N WG 12S 35 CM</t>
-  </si>
-  <si>
-    <t>10032895</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT GW 11/35</t>
-  </si>
-  <si>
-    <t>10005974</t>
-  </si>
-  <si>
-    <t>CHARM NIGHT WG 9S/29</t>
-  </si>
-  <si>
-    <t>20140120</t>
-  </si>
-  <si>
-    <t>SOFTX BRY COOL 36-8S</t>
-  </si>
-  <si>
-    <t>20113228</t>
-  </si>
-  <si>
-    <t>SOFTEX DS 3IN1 16'S</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -598,15 +598,24 @@
     <t>IDM TISU ROL 8'S</t>
   </si>
   <si>
+    <t>20142611</t>
+  </si>
+  <si>
+    <t>IDM ALCHOL WIPE2X10S</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
     <t>20141206</t>
   </si>
   <si>
     <t>LARISST MN PCK 8X8'S</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>20140679</t>
   </si>
   <si>
@@ -635,15 +644,6 @@
   </si>
   <si>
     <t>WATERU WHT BMBOO 50S</t>
-  </si>
-  <si>
-    <t>20142611</t>
-  </si>
-  <si>
-    <t>IDM ALCHOL WIPE2X10S</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
   </si>
   <si>
     <t>20098520</t>
@@ -1637,7 +1637,7 @@
         <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
         <v>18</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1737,15 +1737,15 @@
         <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1757,7 +1757,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1777,7 +1777,7 @@
         <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1797,7 +1797,7 @@
         <v>44</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1817,7 +1817,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1857,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,7 +1937,7 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1977,7 +1977,7 @@
         <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1997,7 +1997,7 @@
         <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2037,7 +2037,7 @@
         <v>44</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,7 +2457,7 @@
         <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2757,7 +2757,7 @@
         <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2937,15 +2937,15 @@
         <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>12</v>
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -2982,10 +2982,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -2997,15 +2997,15 @@
         <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3037,15 +3037,15 @@
         <v>44</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>146</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3057,7 +3057,7 @@
         <v>47</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>210</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">

--- a/PPT03D.xlsx
+++ b/PPT03D.xlsx
@@ -454,15 +454,21 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
+    <t>20140120</t>
+  </si>
+  <si>
+    <t>SOFTX BRY COOL 36-8S</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>20114105</t>
   </si>
   <si>
     <t>CHRM CL.FRSH 6S 42CM</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>20099396</t>
   </si>
   <si>
@@ -475,6 +481,12 @@
     <t>CHARM CL.FRSH NW 10S</t>
   </si>
   <si>
+    <t>20140121</t>
+  </si>
+  <si>
+    <t>SOFTX BR.COOL 23-14S</t>
+  </si>
+  <si>
     <t>20091792</t>
   </si>
   <si>
@@ -493,12 +505,6 @@
     <t>CHRM COOL.FRSH WG14S</t>
   </si>
   <si>
-    <t>20140121</t>
-  </si>
-  <si>
-    <t>SOFTX BR.COOL 23-14S</t>
-  </si>
-  <si>
     <t>20017043</t>
   </si>
   <si>
@@ -530,12 +536,6 @@
   </si>
   <si>
     <t>CHARM NIGHT WG 9S/29</t>
-  </si>
-  <si>
-    <t>20140120</t>
-  </si>
-  <si>
-    <t>SOFTX BRY COOL 36-8S</t>
   </si>
   <si>
     <t>20140420</t>
@@ -2497,7 +2497,7 @@
         <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2577,7 +2577,7 @@
         <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2597,7 +2597,7 @@
         <v>44</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2617,7 +2617,7 @@
         <v>47</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2631,30 +2631,30 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2671,10 +2671,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2691,10 +2691,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2711,10 +2711,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2731,13 +2731,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
